--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="60">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,33 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
@@ -100,6 +127,33 @@
     <t>TLAXCALTECA</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -107,6 +161,39 @@
   </si>
   <si>
     <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>ZURY BETZABE</t>
+  </si>
+  <si>
+    <t>NUBIA NAHOMI</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ANDREA YONETH</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
   </si>
   <si>
     <t>MILKA SARAY</t>
@@ -1028,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1066,10 +1153,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1089,10 +1176,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1106,24 +1193,277 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920140</v>
+        <v>21330051920034</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920038</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920041</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920043</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920045</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920047</v>
+      </c>
+      <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920050</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920051</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920055</v>
+      </c>
+      <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920056</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920065</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920140</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
         <v>15</v>
       </c>
-      <c r="G4">
+      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -85,118 +85,46 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
     <t>TLAXCALTECA</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
     <t>CLAUDIA</t>
   </si>
   <si>
     <t>MARIANA</t>
   </si>
   <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
-  </si>
-  <si>
-    <t>NUBIA NAHOMI</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ANDREA YONETH</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
   </si>
 </sst>
 </file>
@@ -597,19 +525,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>63.33</v>
+        <v>93.33</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -623,19 +551,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>58.06</v>
+        <v>61.29</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -649,7 +577,7 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -701,16 +629,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>89.29000000000001</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -724,19 +655,19 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>64.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -792,7 +723,7 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -815,7 +746,7 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -884,7 +815,7 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -907,7 +838,7 @@
         <v>14</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -966,19 +897,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>63.33</v>
+        <v>93.33</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -992,19 +923,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>58.06</v>
+        <v>61.29</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1018,10 +949,10 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -1030,7 +961,7 @@
         <v>90.91</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1070,16 +1001,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>89.29000000000001</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1093,19 +1027,19 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>64.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1115,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1147,22 +1081,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920122</v>
+        <v>21330051920023</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1170,16 +1104,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>18330051920377</v>
+        <v>21330051920122</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1193,22 +1127,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920034</v>
+        <v>18330051920377</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1216,254 +1150,47 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920038</v>
+        <v>20330051920078</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920041</v>
+        <v>21330051920379</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920043</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920045</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920047</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920050</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920051</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920055</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920056</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920065</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920140</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,9 @@
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -100,6 +103,9 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -113,6 +119,9 @@
   </si>
   <si>
     <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
   </si>
   <si>
     <t>CLAUDIA</t>
@@ -1049,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1087,10 +1096,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1104,16 +1113,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920122</v>
+        <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1127,16 +1136,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>18330051920377</v>
+        <v>21330051920122</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1150,39 +1159,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920078</v>
+        <v>18330051920377</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920379</v>
+        <v>20330051920078</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1191,6 +1200,29 @@
         <v>11</v>
       </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920379</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -583,10 +583,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -595,7 +595,7 @@
         <v>30</v>
       </c>
       <c r="G4">
-        <v>90.91</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H4">
         <v>7.3</v>
@@ -635,10 +635,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -647,7 +647,7 @@
         <v>25</v>
       </c>
       <c r="G6">
-        <v>89.29000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H6">
         <v>7.7</v>
@@ -772,10 +772,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>32</v>
@@ -818,10 +818,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>28</v>
@@ -955,10 +955,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -967,7 +967,7 @@
         <v>30</v>
       </c>
       <c r="G4">
-        <v>90.91</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H4">
         <v>7.2</v>
@@ -1007,10 +1007,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="G6">
-        <v>89.29000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H6">
         <v>7.7</v>

--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -91,12 +91,6 @@
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -106,12 +100,6 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -122,12 +110,6 @@
   </si>
   <si>
     <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
   </si>
   <si>
     <t>DULIAM</t>
@@ -1058,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1096,10 +1078,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1119,10 +1101,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1136,93 +1118,47 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920122</v>
+        <v>20330051920078</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>18330051920377</v>
+        <v>21330051920379</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920078</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920379</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -88,18 +88,12 @@
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -107,9 +101,6 @@
   </si>
   <si>
     <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
   </si>
   <si>
     <t>DULIAM</t>
@@ -1040,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1078,10 +1069,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1095,39 +1086,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920111</v>
+        <v>20330051920078</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920078</v>
+        <v>21330051920379</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1136,29 +1127,6 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920379</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -88,12 +88,18 @@
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -101,6 +107,9 @@
   </si>
   <si>
     <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>CITLALI ESPERANZA</t>
   </si>
   <si>
     <t>DULIAM</t>
@@ -1031,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1069,10 +1078,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1086,39 +1095,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920078</v>
+        <v>21330051920101</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920379</v>
+        <v>20330051920078</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1127,6 +1136,29 @@
         <v>11</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920379</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -85,34 +85,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>NEMESIO NAHIM</t>
+    <t>DULIAM</t>
   </si>
   <si>
     <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
   </si>
   <si>
     <t>MIGUEL</t>
@@ -711,16 +705,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>86.67</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -734,16 +731,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>58.06</v>
+      </c>
+      <c r="H3">
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -757,16 +757,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>32</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>94.12</v>
+      </c>
+      <c r="H4">
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -780,16 +783,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="H5">
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -803,16 +809,19 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>82.76000000000001</v>
+      </c>
+      <c r="H6">
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -826,16 +835,19 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H7">
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -891,16 +903,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>93.33</v>
+        <v>86.67</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -917,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>61.29</v>
+        <v>58.06</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -943,16 +955,16 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -978,7 +990,7 @@
         <v>60</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -995,16 +1007,16 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>86.20999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1021,16 +1033,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -1040,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1072,16 +1084,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920023</v>
+        <v>20330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1104,7 +1116,7 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1118,7 +1130,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920078</v>
+        <v>21330051920379</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1127,7 +1139,7 @@
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1136,29 +1148,6 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920379</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -88,25 +88,16 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>DULIAM</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
   </si>
   <si>
     <t>MIGUEL</t>
@@ -562,16 +553,16 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4">
         <v>7.3</v>
@@ -614,16 +605,16 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>86.20999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="H6">
         <v>7.7</v>
@@ -757,16 +748,16 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H4">
         <v>7.3</v>
@@ -783,19 +774,19 @@
         <v>25</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
         <v>13</v>
       </c>
-      <c r="E5">
-        <v>13</v>
-      </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
       <c r="G5">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -809,16 +800,16 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>82.76000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H6">
         <v>7.8</v>
@@ -952,16 +943,16 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H4">
         <v>7.5</v>
@@ -981,16 +972,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1004,19 +995,19 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>82.76000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1052,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1090,10 +1081,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1107,47 +1098,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920101</v>
+        <v>21330051920379</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920379</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -85,16 +85,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
   </si>
   <si>
     <t>DULIAM</t>
@@ -1043,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1075,16 +1099,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920078</v>
+        <v>21330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1098,7 +1122,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920379</v>
+        <v>21330051920023</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1107,7 +1131,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1116,6 +1140,75 @@
         <v>11</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920122</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920078</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920379</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -85,46 +85,55 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>ZURY BETZABE</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
   </si>
 </sst>
 </file>
@@ -918,16 +927,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -944,16 +953,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>58.06</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -979,7 +988,7 @@
         <v>97.06</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -996,16 +1005,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1022,16 +1031,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>86.20999999999999</v>
+        <v>55.17</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1048,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>92.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1099,22 +1108,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920003</v>
+        <v>21330051920390</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1122,22 +1131,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920023</v>
+        <v>21330051920067</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1145,45 +1154,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920122</v>
+        <v>21330051920034</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920078</v>
+        <v>21330051920045</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1191,24 +1200,47 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920379</v>
+        <v>21330051920046</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920065</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -103,6 +106,9 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
     <t>CELESTINO</t>
   </si>
   <si>
@@ -116,6 +122,9 @@
   </si>
   <si>
     <t>SIERRA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
   </si>
   <si>
     <t>KARLA JIMENA</t>
@@ -1076,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1108,22 +1117,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920390</v>
+        <v>20330051920089</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1131,16 +1140,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920067</v>
+        <v>21330051920390</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1154,16 +1163,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920034</v>
+        <v>21330051920067</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1172,21 +1181,21 @@
         <v>14</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920045</v>
+        <v>21330051920034</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1200,16 +1209,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920046</v>
+        <v>21330051920045</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1223,16 +1232,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920065</v>
+        <v>21330051920046</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1241,6 +1250,29 @@
         <v>14</v>
       </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920065</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,9 @@
     <t>MIXCOHA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -125,6 +128,9 @@
   </si>
   <si>
     <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
   </si>
   <si>
     <t>KARLA JIMENA</t>
@@ -1085,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1123,10 +1129,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1140,22 +1146,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920390</v>
+        <v>21330051920125</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1163,7 +1169,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920067</v>
+        <v>21330051920390</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1172,7 +1178,7 @@
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1186,7 +1192,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920034</v>
+        <v>21330051920067</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1195,7 +1201,7 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1204,12 +1210,12 @@
         <v>14</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920045</v>
+        <v>21330051920034</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1218,7 +1224,7 @@
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1232,7 +1238,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920046</v>
+        <v>21330051920045</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -1241,7 +1247,7 @@
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1255,16 +1261,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920065</v>
+        <v>21330051920046</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1273,6 +1279,29 @@
         <v>14</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920065</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>
